--- a/sources/wang_step3.xlsx
+++ b/sources/wang_step3.xlsx
@@ -732,6 +732,11 @@
           <t>Crouch</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
@@ -769,6 +774,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
@@ -806,6 +816,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
@@ -841,6 +856,11 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0bbb7217-3bd9-4aa5-bd95-cfe77d966840</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4169,6 +4189,11 @@
       <c r="I81" t="inlineStr">
         <is>
           <t>hmmhlmhhLm</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>f2b1b105-8e73-4505-9cf6-fc48f600c675</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
